--- a/data/overtheyears.xlsx
+++ b/data/overtheyears.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\EFSPI\20_workshop\efspiworkshop\workshop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B028BABA-7BA1-4288-BC66-0524204ADFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED7648E-8076-42C0-9F59-239B2518C8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>F2F</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Year</t>
+  </si>
+  <si>
+    <t>Paying</t>
   </si>
 </sst>
 </file>
@@ -368,10 +371,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -387,8 +390,11 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -405,7 +411,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -422,7 +428,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -439,7 +445,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -455,8 +461,11 @@
       <c r="E5">
         <v>56</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -471,6 +480,29 @@
       </c>
       <c r="E6">
         <v>63</v>
+      </c>
+      <c r="F6">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>115</v>
+      </c>
+      <c r="C7">
+        <v>187</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/data/overtheyears.xlsx
+++ b/data/overtheyears.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\EFSPI\20_workshop\efspiworkshop\workshop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED7648E-8076-42C0-9F59-239B2518C8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76334D0A-ACE7-45ED-B261-F01F1179D0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -490,19 +490,19 @@
         <v>2026</v>
       </c>
       <c r="B7">
-        <v>115</v>
+        <v>229</v>
       </c>
       <c r="C7">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>61</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/data/overtheyears.xlsx
+++ b/data/overtheyears.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\EFSPI\20_workshop\efspiworkshop\workshop\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\efspieurope\workshop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76334D0A-ACE7-45ED-B261-F01F1179D0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E164D4-4ED2-424C-965D-753F85DFDF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -372,9 +372,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -394,7 +394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -411,7 +411,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -428,7 +428,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -445,7 +445,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -465,7 +465,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -485,24 +485,24 @@
         <v>325</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2026</v>
       </c>
       <c r="B7">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C7">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/overtheyears.xlsx
+++ b/data/overtheyears.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\efspieurope\workshop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E164D4-4ED2-424C-965D-753F85DFDF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB53CDA0-AD9B-498C-AB8E-913B30ED1F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1480" yWindow="1480" windowWidth="13640" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -373,6 +373,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -490,19 +498,19 @@
         <v>2026</v>
       </c>
       <c r="B7">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="C7">
-        <v>281</v>
+        <v>250</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/data/overtheyears.xlsx
+++ b/data/overtheyears.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\efspieurope\workshop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB53CDA0-AD9B-498C-AB8E-913B30ED1F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7386A4E8-5B3B-487C-9282-F10FC3B4197F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="13640" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -498,19 +498,19 @@
         <v>2026</v>
       </c>
       <c r="B7">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C7">
-        <v>250</v>
+        <v>331</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F7">
-        <v>141</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
